--- a/workspace/Health Facility Data/WyomingHealth24_xlsx.xlsx
+++ b/workspace/Health Facility Data/WyomingHealth24_xlsx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c1929351461b30c/Documents/internship/workspace/Health Facility Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{8300B9D4-235B-4A3B-8321-9D473C3F3D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996B95F3-6EE6-4911-88A6-EB0660A3C09A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{8300B9D4-235B-4A3B-8321-9D473C3F3D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91972708-87BE-4020-9AE0-42A281982644}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{298DB5C7-3C3B-4842-B707-6D8D22690268}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{298DB5C7-3C3B-4842-B707-6D8D22690268}"/>
   </bookViews>
   <sheets>
     <sheet name="WyomingHealth24" sheetId="1" r:id="rId1"/>
@@ -2162,6 +2162,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2481,6 +2485,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71375850-C0B6-44FF-A853-C38544CA859A}">
   <dimension ref="A1:C279"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
